--- a/FP403_task4_result.xlsx
+++ b/FP403_task4_result.xlsx
@@ -9,7 +9,16 @@
   <sheets>
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="FloorPlan403_R1" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="FloorPlan403_Avg" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="FloorPlan403_R2" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="FloorPlan403_R3" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="FloorPlan403_R4" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="FloorPlan403_R5" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="FloorPlan403_R6" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="FloorPlan403_R7" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="FloorPlan403_R8" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="FloorPlan403_R9" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="FloorPlan403_R10" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="FloorPlan403_Avg" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -493,16 +502,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4">
@@ -512,16 +521,16 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -529,13 +538,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -566,18 +575,92 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Put Plunger in the cabinet and Put the</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>50</v>
+      </c>
+      <c r="D2" t="n">
+        <v>50</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Physical Guard GCR (%)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Baseline GCR (%)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>차이 (PG - BL)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Put Plunger in the cabinet and Put the</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>50</v>
+      </c>
+      <c r="D2" t="n">
+        <v>50</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -620,20 +703,510 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Put Plunger in the cabinet and Put the</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>50</v>
+      </c>
+      <c r="D2" t="n">
+        <v>50</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>50.0, 50.0, 50.0, 50.0, 50.0, 50.0, 50.0, 50.0, 50.0, 50.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Scene 평균</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>0</v>
+      <c r="B4" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>50</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Physical Guard GCR (%)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Baseline GCR (%)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>차이 (PG - BL)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Put Plunger in the cabinet and Put the</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>50</v>
+      </c>
+      <c r="D2" t="n">
+        <v>50</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Physical Guard GCR (%)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Baseline GCR (%)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>차이 (PG - BL)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Put Plunger in the cabinet and Put the</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>50</v>
+      </c>
+      <c r="D2" t="n">
+        <v>50</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Physical Guard GCR (%)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Baseline GCR (%)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>차이 (PG - BL)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Put Plunger in the cabinet and Put the</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>50</v>
+      </c>
+      <c r="D2" t="n">
+        <v>50</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Physical Guard GCR (%)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Baseline GCR (%)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>차이 (PG - BL)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Put Plunger in the cabinet and Put the</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>50</v>
+      </c>
+      <c r="D2" t="n">
+        <v>50</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Physical Guard GCR (%)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Baseline GCR (%)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>차이 (PG - BL)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Put Plunger in the cabinet and Put the</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>50</v>
+      </c>
+      <c r="D2" t="n">
+        <v>50</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Physical Guard GCR (%)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Baseline GCR (%)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>차이 (PG - BL)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Put Plunger in the cabinet and Put the</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>50</v>
+      </c>
+      <c r="D2" t="n">
+        <v>50</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Physical Guard GCR (%)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Baseline GCR (%)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>차이 (PG - BL)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Put Plunger in the cabinet and Put the</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>50</v>
+      </c>
+      <c r="D2" t="n">
+        <v>50</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Physical Guard GCR (%)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Baseline GCR (%)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>차이 (PG - BL)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Put Plunger in the cabinet and Put the</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>50</v>
+      </c>
+      <c r="D2" t="n">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
